--- a/filtered_questions.xlsx
+++ b/filtered_questions.xlsx
@@ -733,8 +733,14 @@
       <c r="O4" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2019,8 +2025,14 @@
       <c r="O20" t="n">
         <v>2.5</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2281,12 +2293,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6406536198116</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>,</t>
@@ -2294,19 +2318,45 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6406536198116</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>naecoocean</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>naecoocean</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Naecoocean</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Naecoocean</t>
+        </is>
+      </c>
       <c r="O24" t="n">
         <v>2.5</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2324,12 +2374,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6406536198117</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>,</t>
@@ -2337,19 +2399,45 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6406536198117</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O25" t="n">
         <v>2.5</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2367,12 +2455,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6406536198118</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>,</t>
@@ -2380,19 +2480,45 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6406536198118</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="O26" t="n">
         <v>2.5</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2410,12 +2536,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6406536198119</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>,</t>
@@ -2423,19 +2561,45 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6406536198119</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>polarpolar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>polarpolar</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>polarpolar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>polarpolar</t>
+        </is>
+      </c>
       <c r="O27" t="n">
         <v>2.5</v>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2453,12 +2617,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6406536198120</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>,</t>
@@ -2466,19 +2642,45 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6406536198120</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O28" t="n">
         <v>2.5</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2496,12 +2698,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6406536198121</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>,</t>
@@ -2509,19 +2723,45 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6406536198121</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="O29" t="n">
         <v>2.5</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2539,12 +2779,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6406536198122</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>,</t>
@@ -2552,19 +2804,45 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6406536198122</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ghjemakbclifd</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ghjemakbclifd</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ghjemakbclifd</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>ghjemakbclifd</t>
+        </is>
+      </c>
       <c r="O30" t="n">
         <v>2.5</v>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2582,12 +2860,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6406536198123</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>,</t>
@@ -2595,19 +2885,45 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6406536198123</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>[(1,2),(2,1),(2,4),(3,0),(3,3),(4,2),(5,1),(5,4)]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[(1,2),(2,1),(2,4),(3,0),(3,3),(4,2),(5,1),(5,4)]</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>[(1,2),(2,1),(2,4),(3,0),(3,3),(4,2),(5,1),(5,4)]</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[(1,2),(2,1),(2,4),(3,0),(3,3),(4,2),(5,1),(5,4)]</t>
+        </is>
+      </c>
       <c r="O31" t="n">
         <v>2.5</v>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2625,12 +2941,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6406536198124</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>,</t>
@@ -2638,19 +2966,45 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6406536198124</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>[6,3,4,8,2,9]</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[6,3,4,8,2,9]</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>[6,3,4,8,2,9]</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>[6,3,4,8,2,9]</t>
+        </is>
+      </c>
       <c r="O32" t="n">
         <v>2.5</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2668,12 +3022,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6406536198125</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>,</t>
@@ -2681,19 +3047,37 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6406536198125</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
         <v>2.5</v>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2711,12 +3095,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6406536198126</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>,</t>
@@ -2724,19 +3120,37 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6406536198126</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
         <v>2.5</v>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2754,12 +3168,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6406536198127</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>,</t>
@@ -2767,19 +3193,37 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6406536198127</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>2.5</v>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2797,12 +3241,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6406536198128</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>,</t>
@@ -2810,19 +3266,37 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6406536198128</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>[9,2,6,1,8,2,6]</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[9,2,6,1,8,2,6]</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
         <v>2.5</v>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2840,12 +3314,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6406536198129</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>,</t>
@@ -2853,19 +3339,37 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6406536198129</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>[9,2,6,1,8,2,6]</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[9,2,6,1,8,2,6]</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
         <v>2.5</v>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2883,12 +3387,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6406536198130</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>,</t>
@@ -2896,19 +3412,37 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6406536198130</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>[9,2,6,1,8,2,6,6,1,8,2]</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[9,2,6,1,8,2,6,6,1,8,2]</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
         <v>2.5</v>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2926,12 +3460,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6406536198131</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>,</t>
@@ -2939,19 +3485,37 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6406536198131</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>[16,18,17,19]</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[16,18,17,19]</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
         <v>2.5</v>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2969,12 +3533,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6406536198132</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>,</t>
@@ -2982,19 +3558,37 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6406536198132</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>[11,17,19]</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[11,17,19]</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
         <v>2.5</v>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3012,12 +3606,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6406536198133</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>,</t>
@@ -3025,19 +3631,37 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6406536198133</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>2.5</v>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
